--- a/PVH.xlsx
+++ b/PVH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D306F3D-D21B-4F37-ADEC-9BDFC7A2A03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F85B7B-7733-458B-BAA3-33110BF0C2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{4E82A43E-637D-4DBB-91B0-A5D722633EBD}"/>
   </bookViews>
@@ -300,6 +300,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -326,12 +332,6 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -471,41 +471,45 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -880,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="7">
-        <v>80.760000000000005</v>
+        <v>77.790000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -888,10 +892,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="4">
-        <v>45.811528000000003</v>
-      </c>
-      <c r="K3" s="23" t="s">
-        <v>54</v>
+        <v>46.108091999999999</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -903,7 +907,7 @@
       </c>
       <c r="J4" s="4">
         <f>+J2*J3</f>
-        <v>3699.7390012800006</v>
+        <v>3586.7484766800003</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -914,10 +918,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="4">
-        <v>701.6</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>54</v>
+        <v>592.5</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -925,11 +929,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <f>0+2291.4</f>
-        <v>2291.4</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>54</v>
+        <f>12.9+2269.4</f>
+        <v>2282.3000000000002</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -944,7 +948,7 @@
       </c>
       <c r="J7" s="4">
         <f>+J4-J5+J6</f>
-        <v>5289.5390012800008</v>
+        <v>5276.54847668</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2294,7 +2298,9 @@
         <v>2294.3000000000002</v>
       </c>
       <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="O15" s="6">
+        <v>2025.1</v>
+      </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
@@ -2408,7 +2414,9 @@
         <v>1001.5</v>
       </c>
       <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="O16" s="4">
+        <v>838.9</v>
+      </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -2528,8 +2536,14 @@
         <f>+M15-M16</f>
         <v>1292.8000000000002</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
+      <c r="N17" s="4">
+        <f>+N15-N16</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="4">
+        <f>+O15-O16</f>
+        <v>1186.1999999999998</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -2645,7 +2659,9 @@
         <v>1121</v>
       </c>
       <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
+      <c r="O18" s="4">
+        <v>1074.4000000000001</v>
+      </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -2763,41 +2779,47 @@
         <v>121.89999999999964</v>
       </c>
       <c r="M19" s="4">
-        <f>+M17-M18</f>
+        <f t="shared" ref="M19:O19" si="6">+M17-M18</f>
         <v>171.80000000000018</v>
       </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
+      <c r="N19" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="6"/>
+        <v>111.79999999999973</v>
+      </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4">
-        <f t="shared" ref="T19" si="6">+T17-T18</f>
+        <f t="shared" ref="T19" si="7">+T17-T18</f>
         <v>0</v>
       </c>
       <c r="U19" s="4">
-        <f t="shared" ref="U19" si="7">+U17-U18</f>
+        <f t="shared" ref="U19" si="8">+U17-U18</f>
         <v>0</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" ref="V19" si="8">+V17-V18</f>
+        <f t="shared" ref="V19" si="9">+V17-V18</f>
         <v>0</v>
       </c>
       <c r="W19" s="4">
-        <f t="shared" ref="W19" si="9">+W17-W18</f>
+        <f t="shared" ref="W19" si="10">+W17-W18</f>
         <v>745.49999999999909</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" ref="X19" si="10">+X17-X18</f>
+        <f t="shared" ref="X19" si="11">+X17-X18</f>
         <v>820.60000000000036</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" ref="Y19:Z19" si="11">+Y17-Y18</f>
+        <f t="shared" ref="Y19:Z19" si="12">+Y17-Y18</f>
         <v>731.20000000000164</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>177</v>
       </c>
       <c r="AA19" s="4"/>
@@ -2882,7 +2904,9 @@
         <v>-1</v>
       </c>
       <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
+      <c r="O20" s="4">
+        <v>-0.8</v>
+      </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
@@ -2985,7 +3009,9 @@
         <v>0</v>
       </c>
       <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
+      <c r="O21" s="4">
+        <v>0</v>
+      </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
@@ -3087,7 +3113,9 @@
         <v>10</v>
       </c>
       <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
+      <c r="O22" s="4">
+        <v>13.3</v>
+      </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
@@ -3189,7 +3217,9 @@
         <v>23.2</v>
       </c>
       <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
+      <c r="O23" s="4">
+        <v>22.7</v>
+      </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
@@ -3291,7 +3321,9 @@
         <v>2.7</v>
       </c>
       <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
+      <c r="O24" s="4">
+        <v>6.9</v>
+      </c>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
@@ -3368,27 +3400,27 @@
         <v>30</v>
       </c>
       <c r="C25" s="4">
-        <f t="shared" ref="C25:H25" si="12">+C19+SUM(C20:C22)-C23+C24</f>
+        <f>+C19+SUM(C20:C22)-C23+C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="4">
-        <f t="shared" si="12"/>
+        <f>+D19+SUM(D20:D22)-D23+D24</f>
         <v>0</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="12"/>
+        <f>+E19+SUM(E20:E22)-E23+E24</f>
         <v>207.60000000000011</v>
       </c>
       <c r="F25" s="4">
-        <f t="shared" si="12"/>
+        <f>+F19+SUM(F20:F22)-F23+F24</f>
         <v>0</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" si="12"/>
+        <f>+G19+SUM(G20:G22)-G23+G24</f>
         <v>187.40000000000006</v>
       </c>
       <c r="H25" s="4">
-        <f t="shared" si="12"/>
+        <f>+H19+SUM(H20:H22)-H23+H24</f>
         <v>154.80000000000013</v>
       </c>
       <c r="I25" s="4">
@@ -3396,53 +3428,59 @@
         <v>166.99999999999991</v>
       </c>
       <c r="J25" s="4">
-        <f t="shared" ref="J25:M25" si="13">+J19+SUM(J20:J22)-J23+J24</f>
+        <f>+J19+SUM(J20:J22)-J23+J24</f>
         <v>0</v>
       </c>
       <c r="K25" s="4">
-        <f t="shared" si="13"/>
+        <f>+K19+SUM(K20:K22)-K23+K24</f>
         <v>-349.60000000000025</v>
       </c>
       <c r="L25" s="4">
-        <f t="shared" si="13"/>
+        <f>+L19+SUM(L20:L22)-L23+L24</f>
         <v>111.19999999999965</v>
       </c>
       <c r="M25" s="4">
-        <f t="shared" si="13"/>
+        <f>+M19+SUM(M20:M22)-M23+M24</f>
         <v>160.30000000000018</v>
       </c>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
+      <c r="N25" s="4">
+        <f>+N19+SUM(N20:N22)-N23+N24</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="4">
+        <f>+O19+SUM(O20:O22)-O23+O24</f>
+        <v>108.49999999999973</v>
+      </c>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4">
-        <f t="shared" ref="T25" si="14">+T19+SUM(T20:T22)-T23+T24</f>
+        <f>+T19+SUM(T20:T22)-T23+T24</f>
         <v>0</v>
       </c>
       <c r="U25" s="4">
-        <f t="shared" ref="U25" si="15">+U19+SUM(U20:U22)-U23+U24</f>
+        <f>+U19+SUM(U20:U22)-U23+U24</f>
         <v>0</v>
       </c>
       <c r="V25" s="4">
-        <f t="shared" ref="V25" si="16">+V19+SUM(V20:V22)-V23+V24</f>
+        <f>+V19+SUM(V20:V22)-V23+V24</f>
         <v>0</v>
       </c>
       <c r="W25" s="4">
-        <f t="shared" ref="W25" si="17">+W19+SUM(W20:W22)-W23+W24</f>
+        <f>+W19+SUM(W20:W22)-W23+W24</f>
         <v>388.19999999999902</v>
       </c>
       <c r="X25" s="4">
-        <f t="shared" ref="X25" si="18">+X19+SUM(X20:X22)-X23+X24</f>
+        <f>+X19+SUM(X20:X22)-X23+X24</f>
         <v>841.00000000000045</v>
       </c>
       <c r="Y25" s="4">
-        <f t="shared" ref="Y25:Z25" si="19">+Y19+SUM(Y20:Y22)-Y23+Y24</f>
+        <f>+Y19+SUM(Y20:Y22)-Y23+Y24</f>
         <v>705.70000000000175</v>
       </c>
       <c r="Z25" s="4">
-        <f t="shared" si="19"/>
+        <f>+Z19+SUM(Z20:Z22)-Z23+Z24</f>
         <v>151.29999999999998</v>
       </c>
       <c r="AA25" s="4"/>
@@ -3527,7 +3565,9 @@
         <v>156.1</v>
       </c>
       <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
+      <c r="O26" s="4">
+        <v>20.5</v>
+      </c>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
@@ -3604,27 +3644,27 @@
         <v>32</v>
       </c>
       <c r="C27" s="4">
-        <f t="shared" ref="C27:H27" si="20">+C25-C26</f>
+        <f t="shared" ref="C27:H27" si="13">+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>161.60000000000011</v>
       </c>
       <c r="F27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>151.40000000000006</v>
       </c>
       <c r="H27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="13"/>
         <v>158.00000000000011</v>
       </c>
       <c r="I27" s="4">
@@ -3632,41 +3672,47 @@
         <v>131.89999999999992</v>
       </c>
       <c r="J27" s="4">
-        <f t="shared" ref="J27:M27" si="21">+J25-J26</f>
+        <f t="shared" ref="J27:N27" si="14">+J25-J26</f>
         <v>0</v>
       </c>
       <c r="K27" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>-44.800000000000239</v>
       </c>
       <c r="L27" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>224.19999999999965</v>
       </c>
       <c r="M27" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="14"/>
         <v>4.2000000000001876</v>
       </c>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
+      <c r="N27" s="4">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <f t="shared" ref="O27" si="15">+O25-O26</f>
+        <v>87.99999999999973</v>
+      </c>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4">
-        <f t="shared" ref="T27:W27" si="22">+T25-T26</f>
+        <f t="shared" ref="T27:W27" si="16">+T25-T26</f>
         <v>0</v>
       </c>
       <c r="U27" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="V27" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="W27" s="4">
-        <f t="shared" si="22"/>
+        <f t="shared" si="16"/>
         <v>200.39999999999901</v>
       </c>
       <c r="X27" s="4">
@@ -3674,11 +3720,11 @@
         <v>723.60000000000048</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" ref="Y27:Z27" si="23">+Y25-Y26</f>
+        <f t="shared" ref="Y27:Z27" si="17">+Y25-Y26</f>
         <v>598.50000000000171</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="17"/>
         <v>25.299999999999983</v>
       </c>
       <c r="AA27" s="4"/>
@@ -3815,11 +3861,11 @@
         <v>33</v>
       </c>
       <c r="C29" s="7" t="e">
-        <f t="shared" ref="C29:D29" si="24">+C27/C30</f>
+        <f t="shared" ref="C29:D29" si="18">+C27/C30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="7" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E29" s="7">
@@ -3827,69 +3873,78 @@
         <v>2.6799336650082939</v>
       </c>
       <c r="F29" s="7" t="e">
-        <f t="shared" ref="F29:M29" si="25">+F27/F30</f>
+        <f t="shared" ref="F29:P29" si="19">+F27/F30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>2.5924657534246585</v>
       </c>
       <c r="H29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>2.7964601769911526</v>
       </c>
       <c r="I29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>2.3637992831541204</v>
       </c>
       <c r="J29" s="7" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>-0.8767123287671279</v>
       </c>
       <c r="L29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>4.6611226611226533</v>
       </c>
       <c r="M29" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="19"/>
         <v>8.8794926004232305E-2</v>
       </c>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
+      <c r="N29" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="7">
+        <f t="shared" si="19"/>
+        <v>1.9172113289760291</v>
+      </c>
+      <c r="P29" s="7" t="e">
+        <f t="shared" si="19"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="8"/>
       <c r="T29" s="7" t="e">
-        <f t="shared" ref="T29:Z29" si="26">+T27/T30</f>
+        <f t="shared" ref="T29:Z29" si="20">+T27/T30</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U29" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V29" s="7" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W29" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>3.0502283105022681</v>
       </c>
       <c r="X29" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>11.86229508196722</v>
       </c>
       <c r="Y29" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>10.68750000000003</v>
       </c>
       <c r="Z29" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="20"/>
         <v>0.52598752598752563</v>
       </c>
       <c r="AA29" s="8"/>
@@ -3948,7 +4003,9 @@
         <v>47.3</v>
       </c>
       <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="O30" s="26">
+        <v>45.9</v>
+      </c>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -4070,20 +4127,29 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="22">
-        <f t="shared" ref="K32:M32" si="27">+K15/G15-1</f>
+        <f>+K15/G15-1</f>
         <v>1.6240586095598974E-2</v>
       </c>
       <c r="L32" s="22">
-        <f t="shared" si="27"/>
+        <f>+L15/H15-1</f>
         <v>4.478619293255548E-2</v>
       </c>
       <c r="M32" s="22">
-        <f t="shared" si="27"/>
+        <f>+M15/I15-1</f>
         <v>1.7382821160924156E-2</v>
       </c>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
+      <c r="N32" s="22" t="e">
+        <f>+N15/J15-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O32" s="22">
+        <f t="shared" ref="O32:P32" si="21">+O15/K15-1</f>
+        <v>2.0921556765476801E-2</v>
+      </c>
+      <c r="P32" s="22">
+        <f t="shared" si="21"/>
+        <v>-1</v>
+      </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="8"/>
@@ -4143,31 +4209,31 @@
         <v>38</v>
       </c>
       <c r="C33" s="9" t="e">
-        <f t="shared" ref="C33:I33" si="28">+C17/C15</f>
+        <f>+C17/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f>+D17/D15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="9">
-        <f t="shared" si="28"/>
+        <f>+E17/E15</f>
         <v>0.56684582504549497</v>
       </c>
       <c r="F33" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f>+F17/F15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" si="28"/>
+        <f>+G17/G15</f>
         <v>0.61411957579794041</v>
       </c>
       <c r="H33" s="9">
-        <f t="shared" si="28"/>
+        <f>+H17/H15</f>
         <v>0.60063635925372416</v>
       </c>
       <c r="I33" s="9">
-        <f t="shared" si="28"/>
+        <f>+I17/I15</f>
         <v>0.58383220256307922</v>
       </c>
       <c r="J33" s="9" t="e">
@@ -4175,46 +4241,55 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" ref="K33:L33" si="29">+K17/K15</f>
+        <f>+K17/K15</f>
         <v>0.58565234926396448</v>
       </c>
       <c r="L33" s="9">
-        <f t="shared" si="29"/>
+        <f>+L17/L15</f>
         <v>0.5771502399409375</v>
       </c>
       <c r="M33" s="9">
-        <f t="shared" ref="M33" si="30">+M17/M15</f>
+        <f>+M17/M15</f>
         <v>0.56348341542082558</v>
       </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="N33" s="9" t="e">
+        <f>+N17/N15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O33" s="9">
+        <f t="shared" ref="O33:P33" si="22">+O17/O15</f>
+        <v>0.58574885190854764</v>
+      </c>
+      <c r="P33" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="9" t="e">
-        <f t="shared" ref="U33:Y33" si="31">+U17/U15</f>
+        <f>+U17/U15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V33" s="9" t="e">
-        <f t="shared" si="31"/>
+        <f>+V17/V15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W33" s="9">
-        <f t="shared" si="31"/>
+        <f>+W17/W15</f>
         <v>0.56768467010926171</v>
       </c>
       <c r="X33" s="9">
-        <f t="shared" si="31"/>
+        <f>+X17/X15</f>
         <v>0.58183711771917079</v>
       </c>
       <c r="Y33" s="9">
-        <f t="shared" si="31"/>
+        <f>+Y17/Y15</f>
         <v>0.59430942227461325</v>
       </c>
       <c r="Z33" s="9">
-        <f t="shared" ref="Z33" si="32">+Z17/Z15</f>
+        <f>+Z17/Z15</f>
         <v>0.57524971509016554</v>
       </c>
       <c r="AA33" s="8"/>
@@ -4248,11 +4323,11 @@
         <v>39</v>
       </c>
       <c r="C34" s="9" t="e">
-        <f t="shared" ref="C34:D34" si="33">+C19/C15</f>
+        <f>+C19/C15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="9" t="e">
-        <f t="shared" si="33"/>
+        <f>+D19/D15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="9">
@@ -4260,66 +4335,75 @@
         <v>9.1243810571755096E-2</v>
       </c>
       <c r="F34" s="9" t="e">
-        <f t="shared" ref="F34:J34" si="34">+F19/F15</f>
+        <f>+F19/F15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="9">
-        <f t="shared" si="34"/>
+        <f>+G19/G15</f>
         <v>9.2935088887750442E-2</v>
       </c>
       <c r="H34" s="9">
-        <f t="shared" si="34"/>
+        <f>+H19/H15</f>
         <v>7.8387889890565554E-2</v>
       </c>
       <c r="I34" s="9">
-        <f t="shared" si="34"/>
+        <f>+I19/I15</f>
         <v>7.2103232672608722E-2</v>
       </c>
       <c r="J34" s="9" t="e">
-        <f t="shared" si="34"/>
+        <f>+J19/J15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="9">
-        <f t="shared" ref="K34:L34" si="35">+K19/K15</f>
+        <f>+K19/K15</f>
         <v>-0.17226255293405943</v>
       </c>
       <c r="L34" s="9">
-        <f t="shared" si="35"/>
+        <f>+L19/L15</f>
         <v>5.6247692875599692E-2</v>
       </c>
       <c r="M34" s="9">
-        <f t="shared" ref="M34" si="36">+M19/M15</f>
+        <f>+M19/M15</f>
         <v>7.4881227389617819E-2</v>
       </c>
-      <c r="N34" s="9"/>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
+      <c r="N34" s="9" t="e">
+        <f>+N19/N15</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="shared" ref="O34:P34" si="23">+O19/O15</f>
+        <v>5.5207150264184351E-2</v>
+      </c>
+      <c r="P34" s="9" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="8"/>
       <c r="T34" s="8"/>
       <c r="U34" s="9" t="e">
-        <f t="shared" ref="U34:Y34" si="37">+U19/U15</f>
+        <f>+U19/U15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V34" s="9" t="e">
-        <f t="shared" si="37"/>
+        <f>+V19/V15</f>
         <v>#DIV/0!</v>
       </c>
       <c r="W34" s="9">
-        <f t="shared" si="37"/>
+        <f>+W19/W15</f>
         <v>8.26112009928857E-2</v>
       </c>
       <c r="X34" s="9">
-        <f t="shared" si="37"/>
+        <f>+X19/X15</f>
         <v>8.9024377013788722E-2</v>
       </c>
       <c r="Y34" s="9">
-        <f t="shared" si="37"/>
+        <f>+Y19/Y15</f>
         <v>8.4503461267320959E-2</v>
       </c>
       <c r="Z34" s="9">
-        <f t="shared" ref="Z34" si="38">+Z19/Z15</f>
+        <f>+Z19/Z15</f>
         <v>1.9776094388952201E-2</v>
       </c>
       <c r="AA34" s="8"/>
@@ -4353,27 +4437,27 @@
         <v>40</v>
       </c>
       <c r="C35" s="9" t="e">
-        <f t="shared" ref="C35:H35" si="39">+C26/C25</f>
+        <f t="shared" ref="C35:H35" si="24">+C26/C25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D35" s="9" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0.22157996146435441</v>
       </c>
       <c r="F35" s="9" t="e">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>0.19210245464247591</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="39"/>
+        <f t="shared" si="24"/>
         <v>-2.0671834625322981E-2</v>
       </c>
       <c r="I35" s="9">
@@ -4381,50 +4465,59 @@
         <v>0.21017964071856299</v>
       </c>
       <c r="J35" s="9" t="e">
-        <f t="shared" ref="J35:L35" si="40">+J26/J25</f>
+        <f t="shared" ref="J35:L35" si="25">+J26/J25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="25"/>
         <v>0.87185354691075456</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="25"/>
         <v>-1.0161870503597155</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" ref="M35" si="41">+M26/M25</f>
+        <f t="shared" ref="M35:N35" si="26">+M26/M25</f>
         <v>0.97379912663755341</v>
       </c>
-      <c r="N35" s="9"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="N35" s="9" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O35" s="9">
+        <f t="shared" ref="O35:P35" si="27">+O26/O25</f>
+        <v>0.18894009216589908</v>
+      </c>
+      <c r="P35" s="9" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="8"/>
       <c r="T35" s="8"/>
       <c r="U35" s="9" t="e">
-        <f t="shared" ref="U35:Y35" si="42">+U26/U25</f>
+        <f t="shared" ref="U35:Y35" si="28">+U26/U25</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V35" s="9" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W35" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>0.48377125193199505</v>
       </c>
       <c r="X35" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>0.13959571938168841</v>
       </c>
       <c r="Y35" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="28"/>
         <v>0.15190590902649814</v>
       </c>
       <c r="Z35" s="9">
-        <f t="shared" ref="Z35" si="43">+Z26/Z25</f>
+        <f t="shared" ref="Z35" si="29">+Z26/Z25</f>
         <v>0.83278255122273637</v>
       </c>
       <c r="AA35" s="8"/>
